--- a/labs/lab-03-pivottables-pivotcharts-and-visuals/data/BrightPath_Recruitment_Metrics.xlsx
+++ b/labs/lab-03-pivottables-pivotcharts-and-visuals/data/BrightPath_Recruitment_Metrics.xlsx
@@ -5068,8 +5068,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Review the four charts on the Charts sheet. For each, tell me which question it answers (Q1 Trend,
-Q2 Comparison, Q3 Funnel, Q4 Efficiency), whether the chart type suits that question, and one improvement. Do not change anything.</t>
+          <t>Review the four charts on the Charts sheet. For each, tell me which question it answers (Q1 Trend, Q2 Comparison, Q3 Funnel, Q4 Efficiency), whether the chart type suits that question, and one improvement. Do not change anything.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-03-pivottables-pivotcharts-and-visuals/data/BrightPath_Recruitment_Metrics.xlsx
+++ b/labs/lab-03-pivottables-pivotcharts-and-visuals/data/BrightPath_Recruitment_Metrics.xlsx
@@ -4654,13 +4654,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>378</v>
+        <v>1735</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>14900</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="3">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>270</v>
+        <v>1308</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6200</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="4">
@@ -4686,13 +4686,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213</v>
+        <v>1035</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>1300</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="5">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>149</v>
+        <v>620</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>8500</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="6">
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>175</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1600</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="7">
@@ -4734,13 +4734,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2400</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="8">
@@ -4750,13 +4750,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>785</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2200</v>
+        <v>9900</v>
       </c>
     </row>
   </sheetData>
